--- a/htr-modele-metier-imagerie/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/htr-modele-metier-imagerie/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:11:30+00:00</t>
+    <t>2025-10-14T08:46:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-modele-metier-imagerie/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
+++ b/htr-modele-metier-imagerie/ig/mappingPersonneStructureRelatedEntityFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-14T08:46:07+00:00</t>
+    <t>2025-10-21T10:48:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
